--- a/test-results/整理版.xlsx
+++ b/test-results/整理版.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="26">
   <si>
     <t>品牌</t>
   </si>
@@ -32,6 +32,9 @@
   </si>
   <si>
     <t>单价</t>
+  </si>
+  <si>
+    <t>物料编码</t>
   </si>
   <si>
     <t>合作供货商</t>
@@ -479,18 +482,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="5" width="20" customWidth="1"/>
     <col min="6" max="6" width="30" customWidth="1"/>
-    <col min="7" max="7" width="20" customWidth="1"/>
-    <col min="8" max="8" width="25" customWidth="1"/>
-    <col min="9" max="9" width="30" customWidth="1"/>
-    <col min="10" max="10" width="55" customWidth="1"/>
+    <col min="7" max="8" width="20" customWidth="1"/>
+    <col min="9" max="9" width="25" customWidth="1"/>
+    <col min="10" max="10" width="30" customWidth="1"/>
+    <col min="11" max="11" width="55" customWidth="1"/>
+    <col min="12" max="14" width="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -521,31 +525,43 @@
       <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>18</v>
@@ -553,38 +569,62 @@
       <c r="J2" s="3" t="s">
         <v>19</v>
       </c>
+      <c r="K2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I3" t="s">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="J3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N3" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J1"/>
+  <autoFilter ref="A1:N1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/test-results/整理版.xlsx
+++ b/test-results/整理版.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="28">
   <si>
     <t>品牌</t>
   </si>
@@ -37,6 +37,9 @@
     <t>物料编码</t>
   </si>
   <si>
+    <t>需求公司</t>
+  </si>
+  <si>
     <t>合作供货商</t>
   </si>
   <si>
@@ -67,13 +70,16 @@
     <t>100</t>
   </si>
   <si>
+    <t>武汉吉利汽车部件有限公司</t>
+  </si>
+  <si>
     <t>示例供货商</t>
   </si>
   <si>
     <t>demo_wechat</t>
   </si>
   <si>
-    <t>示例供货商；CNY；含税；运费另计；有效至 2099-12-31</t>
+    <t>手动填写，计价条件待确认</t>
   </si>
   <si>
     <t>待查品牌</t>
@@ -482,19 +488,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:O3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="5" width="20" customWidth="1"/>
     <col min="6" max="6" width="30" customWidth="1"/>
-    <col min="7" max="8" width="20" customWidth="1"/>
-    <col min="9" max="9" width="25" customWidth="1"/>
-    <col min="10" max="10" width="30" customWidth="1"/>
-    <col min="11" max="11" width="55" customWidth="1"/>
-    <col min="12" max="14" width="25" customWidth="1"/>
+    <col min="7" max="9" width="20" customWidth="1"/>
+    <col min="10" max="10" width="25" customWidth="1"/>
+    <col min="11" max="11" width="30" customWidth="1"/>
+    <col min="12" max="12" width="55" customWidth="1"/>
+    <col min="13" max="15" width="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -529,7 +535,7 @@
         <v>10</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="M1" s="2" t="s">
         <v>9</v>
@@ -537,94 +543,103 @@
       <c r="N1" s="2" t="s">
         <v>10</v>
       </c>
+      <c r="O1" s="2" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3" t="s">
         <v>19</v>
       </c>
-      <c r="K2" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I3" t="s">
-        <v>16</v>
-      </c>
       <c r="J3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L3" t="s">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="K3" t="s">
+        <v>17</v>
       </c>
       <c r="M3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N3" t="s">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="O3" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N1"/>
+  <autoFilter ref="A1:O1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/test-results/整理版.xlsx
+++ b/test-results/整理版.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="26">
   <si>
     <t>品牌</t>
   </si>
@@ -67,9 +67,6 @@
     <t/>
   </si>
   <si>
-    <t>100</t>
-  </si>
-  <si>
     <t>武汉吉利汽车部件有限公司</t>
   </si>
   <si>
@@ -77,9 +74,6 @@
   </si>
   <si>
     <t>demo_wechat</t>
-  </si>
-  <si>
-    <t>手动填写，计价条件待确认</t>
   </si>
   <si>
     <t>待查品牌</t>
@@ -567,22 +561,19 @@
         <v>17</v>
       </c>
       <c r="G2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="H2" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I2" s="3" t="s">
+      <c r="J2" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="K2" s="3" t="s">
         <v>20</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>22</v>
       </c>
       <c r="M2" s="3" t="s">
         <v>17</v>
@@ -596,20 +587,20 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" t="s">
         <v>23</v>
       </c>
-      <c r="B3" t="s">
+      <c r="D3" t="s">
         <v>24</v>
       </c>
-      <c r="C3" t="s">
+      <c r="E3" t="s">
         <v>25</v>
       </c>
-      <c r="D3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E3" t="s">
-        <v>27</v>
-      </c>
       <c r="F3" t="s">
         <v>17</v>
       </c>
@@ -620,7 +611,7 @@
         <v>17</v>
       </c>
       <c r="I3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J3" t="s">
         <v>17</v>
